--- a/excel/output_stats_sfvv/ludcmp/EfficiencyStats.xlsx
+++ b/excel/output_stats_sfvv/ludcmp/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-52.4796</v>
+        <v>40.6204</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.81295</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.38932</v>
+        <v>40.6204</v>
       </c>
       <c r="F2" t="n">
         <v>356.3</v>
       </c>
       <c r="G2" t="n">
-        <v>357.29</v>
+        <v>362.28</v>
       </c>
       <c r="H2" t="n">
         <v>332.99</v>
       </c>
       <c r="I2" t="n">
-        <v>331.573</v>
+        <v>333.295</v>
       </c>
       <c r="J2" t="n">
-        <v>59637200000</v>
+        <v>88812600000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
